--- a/development/one_file_rosetta_output/CPCT02010408T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/CPCT02010408T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E526"/>
+  <dimension ref="A1:F526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -510,7 +519,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -678,7 +696,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -706,7 +727,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -732,9 +756,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -795,9 +822,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
         <v>2</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -858,9 +888,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -921,9 +954,12 @@
         </is>
       </c>
       <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -994,7 +1030,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1022,7 +1061,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1050,7 +1092,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1158,7 +1203,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1272,9 +1320,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1300,9 +1351,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1356,9 +1410,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>4</v>
+      </c>
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1412,9 +1469,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1440,9 +1500,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1505,7 +1568,10 @@
       <c r="D21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1533,7 +1599,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1634,7 +1703,10 @@
       <c r="D23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1662,7 +1734,10 @@
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1770,7 +1845,10 @@
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1876,9 +1954,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>2</v>
+      </c>
+      <c r="E26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1934,7 +2015,10 @@
       <c r="D27" s="4">
         <v>2</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1988,9 +2072,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2044,9 +2131,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2100,9 +2190,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2163,9 +2256,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4">
         <v>2</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2226,9 +2322,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
         <v>3</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2291,7 +2390,10 @@
       <c r="D33" s="4">
         <v>4</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2354,7 +2456,10 @@
       <c r="D34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2415,9 +2520,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2443,9 +2551,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2516,7 +2627,10 @@
       <c r="D37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2587,7 +2701,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2658,7 +2775,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2686,7 +2806,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2714,7 +2837,10 @@
       <c r="D41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2740,9 +2866,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2798,7 +2927,10 @@
       <c r="D43" s="4">
         <v>2</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>2</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2852,9 +2984,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2917,7 +3052,10 @@
       <c r="D45" s="4">
         <v>2</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>2</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2980,7 +3118,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3041,9 +3182,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>3</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3104,9 +3248,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>3</v>
+      </c>
+      <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3167,9 +3314,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>3</v>
+      </c>
+      <c r="E49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3238,9 +3388,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>3</v>
+      </c>
+      <c r="E50" s="4">
         <v>2</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3311,7 +3464,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3380,9 +3536,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3460,7 +3619,10 @@
       <c r="D53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3538,7 +3700,10 @@
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3616,7 +3781,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3700,9 +3868,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>2</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3730,7 +3901,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3823,7 +3997,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3851,7 +4028,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3965,9 +4145,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4023,7 +4206,10 @@
       <c r="D61" s="4">
         <v>2</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4077,9 +4263,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>2</v>
+      </c>
+      <c r="E62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4105,9 +4294,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>5</v>
+      </c>
+      <c r="E63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4161,9 +4353,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4">
         <v>2</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4217,9 +4412,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>5</v>
+      </c>
+      <c r="E65" s="4">
         <v>3</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4273,9 +4471,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>5</v>
+      </c>
+      <c r="E66" s="4">
         <v>4</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4331,7 +4532,10 @@
       <c r="D67" s="4">
         <v>5</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>5</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4387,7 +4591,10 @@
       <c r="D68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4448,9 +4655,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>2</v>
+      </c>
+      <c r="E69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4513,7 +4723,10 @@
       <c r="D70" s="4">
         <v>2</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>2</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4576,7 +4789,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4645,9 +4861,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>3</v>
+      </c>
+      <c r="E72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4718,7 +4937,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4787,9 +5009,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>2</v>
+      </c>
+      <c r="E74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4875,7 +5100,10 @@
       <c r="D75" s="4">
         <v>2</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>2</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4961,7 +5189,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5047,7 +5278,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5075,7 +5309,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5103,7 +5340,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5129,9 +5369,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5187,7 +5430,10 @@
       <c r="D81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5213,9 +5459,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>2</v>
+      </c>
+      <c r="E82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5271,7 +5520,10 @@
       <c r="D83" s="4">
         <v>2</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>2</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5325,9 +5577,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>2</v>
+      </c>
+      <c r="E84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5398,7 +5653,10 @@
       <c r="D85" s="4">
         <v>2</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="4">
+        <v>2</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5469,7 +5727,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5540,7 +5801,10 @@
       <c r="D87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5618,7 +5882,10 @@
       <c r="D88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5704,7 +5971,10 @@
       <c r="D89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5732,7 +6002,10 @@
       <c r="D90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5760,7 +6033,10 @@
       <c r="D91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5851,9 +6127,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5954,7 +6233,10 @@
       <c r="D93" s="4">
         <v>2</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6055,7 +6337,10 @@
       <c r="D94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6156,7 +6441,10 @@
       <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6184,7 +6472,10 @@
       <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6300,7 +6591,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6354,9 +6648,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>2</v>
+      </c>
+      <c r="E98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6384,7 +6681,10 @@
       <c r="D99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6447,7 +6747,10 @@
       <c r="D100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6475,7 +6778,10 @@
       <c r="D101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6546,7 +6852,10 @@
       <c r="D102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6654,7 +6963,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6725,7 +7037,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6753,7 +7068,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6869,7 +7187,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6992,7 +7313,10 @@
       <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7020,7 +7344,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7081,9 +7408,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7154,7 +7484,10 @@
       <c r="D110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7240,7 +7573,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7268,7 +7604,10 @@
       <c r="D112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7376,7 +7715,10 @@
       <c r="D113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7404,7 +7746,10 @@
       <c r="D114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="4">
+        <v>1</v>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7520,7 +7865,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7546,9 +7894,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>2</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7602,9 +7953,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>3</v>
+      </c>
+      <c r="E117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7665,9 +8019,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>2</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7730,7 +8087,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7793,7 +8153,10 @@
       <c r="D120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4">
+        <v>1</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7856,7 +8219,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7927,7 +8293,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7955,7 +8324,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7983,7 +8355,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8011,7 +8386,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8039,7 +8417,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8130,9 +8511,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>2</v>
+      </c>
+      <c r="E127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8223,9 +8607,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>2</v>
+      </c>
+      <c r="E128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8253,7 +8640,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8354,7 +8744,10 @@
       <c r="D130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8455,7 +8848,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8561,9 +8957,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>2</v>
+      </c>
+      <c r="E132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8669,9 +9068,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>2</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8697,9 +9099,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>4</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8813,9 +9218,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>4</v>
+      </c>
+      <c r="E135" s="4">
         <v>2</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8929,9 +9337,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8959,7 +9370,10 @@
       <c r="D137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9073,9 +9487,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>2</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9101,9 +9518,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>6</v>
+      </c>
+      <c r="E139" s="4">
         <v>1</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9224,9 +9644,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>6</v>
+      </c>
+      <c r="E140" s="4">
         <v>2</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9347,9 +9770,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>6</v>
+      </c>
+      <c r="E141" s="4">
         <v>3</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9470,9 +9896,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>6</v>
+      </c>
+      <c r="E142" s="4">
         <v>4</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9595,7 +10024,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9623,7 +10055,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9677,9 +10112,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>2</v>
+      </c>
+      <c r="E145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9707,7 +10145,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9778,7 +10219,10 @@
       <c r="D147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9806,7 +10250,10 @@
       <c r="D148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9834,7 +10281,10 @@
       <c r="D149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="4">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9912,7 +10362,10 @@
       <c r="D150" s="4">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>1</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9996,9 +10449,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>2</v>
+      </c>
+      <c r="E151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10091,7 +10547,10 @@
       <c r="D152" s="4">
         <v>2</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>2</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10184,7 +10643,10 @@
       <c r="D153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="4">
+        <v>1</v>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10285,7 +10747,10 @@
       <c r="D154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10311,9 +10776,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>3</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10419,9 +10887,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>3</v>
+      </c>
+      <c r="E156" s="4">
         <v>2</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10529,7 +11000,10 @@
       <c r="D157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10557,7 +11031,10 @@
       <c r="D158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="E158" s="4">
+        <v>1</v>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10671,9 +11148,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10787,9 +11267,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>3</v>
+      </c>
+      <c r="E160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10910,9 +11393,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>3</v>
+      </c>
+      <c r="E161" s="4">
         <v>2</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11035,7 +11521,10 @@
       <c r="D162" s="4">
         <v>3</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="4">
+        <v>3</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11156,9 +11645,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>2</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11279,9 +11771,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>2</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11404,7 +11899,10 @@
       <c r="D165" s="4">
         <v>2</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>2</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11527,7 +12025,10 @@
       <c r="D166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="4">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11590,7 +12091,10 @@
       <c r="D167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11651,9 +12155,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>2</v>
+      </c>
+      <c r="E168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11724,7 +12231,10 @@
       <c r="D169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="4">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11802,7 +12312,10 @@
       <c r="D170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="4">
+        <v>1</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11880,7 +12393,10 @@
       <c r="D171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11908,7 +12424,10 @@
       <c r="D172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="4">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11999,9 +12518,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>2</v>
+      </c>
+      <c r="E173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12102,7 +12624,10 @@
       <c r="D174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="4">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12203,7 +12728,10 @@
       <c r="D175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E175" s="4">
+        <v>1</v>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12231,7 +12759,10 @@
       <c r="D176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12339,7 +12870,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12365,9 +12899,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>2</v>
+      </c>
+      <c r="E178" s="4">
         <v>1</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12423,7 +12960,10 @@
       <c r="D179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="4">
+        <v>1</v>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12479,7 +13019,10 @@
       <c r="D180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>1</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12535,7 +13078,10 @@
       <c r="D181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="4">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12591,7 +13137,10 @@
       <c r="D182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="4">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12645,9 +13194,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>3</v>
+      </c>
+      <c r="E183" s="4">
         <v>1</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12701,9 +13253,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>3</v>
+      </c>
+      <c r="E184" s="4">
         <v>2</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12759,7 +13314,10 @@
       <c r="D185" s="4">
         <v>3</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>3</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12813,9 +13371,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>5</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12869,9 +13430,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>5</v>
+      </c>
+      <c r="E187" s="4">
         <v>2</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12925,9 +13489,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>5</v>
+      </c>
+      <c r="E188" s="4">
         <v>3</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12981,9 +13548,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>5</v>
+      </c>
+      <c r="E189" s="4">
         <v>4</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13039,7 +13609,10 @@
       <c r="D190" s="4">
         <v>5</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="4">
+        <v>5</v>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13093,9 +13666,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>2</v>
+      </c>
+      <c r="E191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13151,7 +13727,10 @@
       <c r="D192" s="4">
         <v>2</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>2</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13205,9 +13784,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>6</v>
+      </c>
+      <c r="E193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13261,9 +13843,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>6</v>
+      </c>
+      <c r="E194" s="4">
         <v>2</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13317,9 +13902,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>6</v>
+      </c>
+      <c r="E195" s="4">
         <v>3</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13373,9 +13961,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>6</v>
+      </c>
+      <c r="E196" s="4">
         <v>4</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13429,9 +14020,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>6</v>
+      </c>
+      <c r="E197" s="4">
         <v>5</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13487,7 +14081,10 @@
       <c r="D198" s="4">
         <v>6</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>6</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13541,9 +14138,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>5</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13597,9 +14197,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>5</v>
+      </c>
+      <c r="E200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13653,9 +14256,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>5</v>
+      </c>
+      <c r="E201" s="4">
         <v>3</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13709,9 +14315,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>2</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13767,7 +14376,10 @@
       <c r="D203" s="4">
         <v>2</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>2</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13821,9 +14433,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>5</v>
+      </c>
+      <c r="E204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13877,9 +14492,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>5</v>
+      </c>
+      <c r="E205" s="4">
         <v>2</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13933,9 +14551,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>5</v>
+      </c>
+      <c r="E206" s="4">
         <v>3</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13989,9 +14610,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>5</v>
+      </c>
+      <c r="E207" s="4">
         <v>4</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14047,7 +14671,10 @@
       <c r="D208" s="4">
         <v>5</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>5</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14101,9 +14728,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>4</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14173,9 +14803,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>4</v>
+      </c>
+      <c r="E210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14245,9 +14878,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>4</v>
+      </c>
+      <c r="E211" s="4">
         <v>3</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14319,7 +14955,10 @@
       <c r="D212" s="4">
         <v>4</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>4</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14389,9 +15028,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>2</v>
+      </c>
+      <c r="E213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14454,7 +15096,10 @@
       <c r="D214" s="4">
         <v>2</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="4">
+        <v>2</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14515,9 +15160,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>6</v>
+      </c>
+      <c r="E215" s="4">
         <v>1</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14616,9 +15264,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>6</v>
+      </c>
+      <c r="E216" s="4">
         <v>2</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14709,9 +15360,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>6</v>
+      </c>
+      <c r="E217" s="4">
         <v>3</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14802,9 +15456,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>6</v>
+      </c>
+      <c r="E218" s="4">
         <v>4</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14880,9 +15537,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>6</v>
+      </c>
+      <c r="E219" s="4">
         <v>5</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14983,7 +15643,10 @@
       <c r="D220" s="4">
         <v>6</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4">
+        <v>6</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15044,9 +15707,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>11</v>
+      </c>
+      <c r="E221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15107,9 +15773,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>11</v>
+      </c>
+      <c r="E222" s="4">
         <v>2</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15170,9 +15839,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>11</v>
+      </c>
+      <c r="E223" s="4">
         <v>3</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15233,9 +15905,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>11</v>
+      </c>
+      <c r="E224" s="4">
         <v>4</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15296,9 +15971,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>11</v>
+      </c>
+      <c r="E225" s="4">
         <v>5</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15359,9 +16037,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>11</v>
+      </c>
+      <c r="E226" s="4">
         <v>6</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15422,9 +16103,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>11</v>
+      </c>
+      <c r="E227" s="4">
         <v>7</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15485,9 +16169,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>11</v>
+      </c>
+      <c r="E228" s="4">
         <v>8</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15548,9 +16235,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>11</v>
+      </c>
+      <c r="E229" s="4">
         <v>9</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15611,9 +16301,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>11</v>
+      </c>
+      <c r="E230" s="4">
         <v>10</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15676,7 +16369,10 @@
       <c r="D231" s="4">
         <v>11</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="4">
+        <v>11</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15739,7 +16435,10 @@
       <c r="D232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="4">
+        <v>1</v>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15808,9 +16507,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>2</v>
+      </c>
+      <c r="E233" s="4">
         <v>1</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15888,7 +16590,10 @@
       <c r="D234" s="4">
         <v>2</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="E234" s="4">
+        <v>2</v>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15964,9 +16669,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>57</v>
+      </c>
+      <c r="E235" s="4">
         <v>1</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16072,9 +16780,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>57</v>
+      </c>
+      <c r="E236" s="4">
         <v>2</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16195,9 +16906,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>57</v>
+      </c>
+      <c r="E237" s="4">
         <v>3</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16356,9 +17070,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>57</v>
+      </c>
+      <c r="E238" s="4">
         <v>4</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16524,9 +17241,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>57</v>
+      </c>
+      <c r="E239" s="4">
         <v>5</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16685,9 +17405,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>57</v>
+      </c>
+      <c r="E240" s="4">
         <v>6</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16838,9 +17561,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>57</v>
+      </c>
+      <c r="E241" s="4">
         <v>7</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16969,9 +17695,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>57</v>
+      </c>
+      <c r="E242" s="4">
         <v>8</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17100,9 +17829,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>57</v>
+      </c>
+      <c r="E243" s="4">
         <v>9</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17186,9 +17918,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>57</v>
+      </c>
+      <c r="E244" s="4">
         <v>10</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17309,9 +18044,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>57</v>
+      </c>
+      <c r="E245" s="4">
         <v>11</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17507,9 +18245,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>57</v>
+      </c>
+      <c r="E246" s="4">
         <v>12</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17683,9 +18424,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>57</v>
+      </c>
+      <c r="E247" s="4">
         <v>13</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17859,9 +18603,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>57</v>
+      </c>
+      <c r="E248" s="4">
         <v>14</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18057,9 +18804,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>57</v>
+      </c>
+      <c r="E249" s="4">
         <v>15</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18188,9 +18938,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>57</v>
+      </c>
+      <c r="E250" s="4">
         <v>16</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18281,9 +19034,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>57</v>
+      </c>
+      <c r="E251" s="4">
         <v>17</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18412,9 +19168,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>57</v>
+      </c>
+      <c r="E252" s="4">
         <v>18</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18550,9 +19309,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>57</v>
+      </c>
+      <c r="E253" s="4">
         <v>19</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18666,9 +19428,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>57</v>
+      </c>
+      <c r="E254" s="4">
         <v>20</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18857,9 +19622,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>4</v>
+      </c>
+      <c r="E255" s="4">
         <v>1</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18920,9 +19688,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>4</v>
+      </c>
+      <c r="E256" s="4">
         <v>2</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18983,9 +19754,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>4</v>
+      </c>
+      <c r="E257" s="4">
         <v>3</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19048,7 +19822,10 @@
       <c r="D258" s="4">
         <v>4</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="E258" s="4">
+        <v>4</v>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19111,7 +19888,10 @@
       <c r="D259" s="4">
         <v>1</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E259" s="4">
+        <v>1</v>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19202,9 +19982,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>2</v>
+      </c>
+      <c r="E260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19276,7 +20059,10 @@
       <c r="D261" s="4">
         <v>2</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="E261" s="4">
+        <v>2</v>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19346,9 +20132,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>2</v>
+      </c>
+      <c r="E262" s="4">
         <v>1</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19479,7 +20268,10 @@
       <c r="D263" s="4">
         <v>2</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="E263" s="4">
+        <v>2</v>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19540,9 +20332,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>11</v>
+      </c>
+      <c r="E264" s="4">
         <v>1</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19603,9 +20398,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>11</v>
+      </c>
+      <c r="E265" s="4">
         <v>2</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19666,9 +20464,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>11</v>
+      </c>
+      <c r="E266" s="4">
         <v>3</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19729,9 +20530,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>11</v>
+      </c>
+      <c r="E267" s="4">
         <v>4</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19792,9 +20596,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>11</v>
+      </c>
+      <c r="E268" s="4">
         <v>5</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19855,9 +20662,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>11</v>
+      </c>
+      <c r="E269" s="4">
         <v>6</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19918,9 +20728,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>11</v>
+      </c>
+      <c r="E270" s="4">
         <v>7</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19981,9 +20794,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>11</v>
+      </c>
+      <c r="E271" s="4">
         <v>8</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20044,9 +20860,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>11</v>
+      </c>
+      <c r="E272" s="4">
         <v>9</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20107,9 +20926,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>11</v>
+      </c>
+      <c r="E273" s="4">
         <v>10</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20172,7 +20994,10 @@
       <c r="D274" s="4">
         <v>11</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="E274" s="4">
+        <v>11</v>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20233,9 +21058,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>2</v>
+      </c>
+      <c r="E275" s="4">
         <v>1</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20306,7 +21134,10 @@
       <c r="D276" s="4">
         <v>2</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="4">
+        <v>2</v>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20377,7 +21208,10 @@
       <c r="D277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="E277" s="4">
+        <v>1</v>
+      </c>
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20453,9 +21287,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>3</v>
+      </c>
+      <c r="E278" s="4">
         <v>1</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20539,9 +21376,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>3</v>
+      </c>
+      <c r="E279" s="4">
         <v>2</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20642,7 +21482,10 @@
       <c r="D280" s="4">
         <v>3</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="4">
+        <v>3</v>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20840,7 +21683,10 @@
       <c r="D281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="4">
+        <v>1</v>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20901,9 +21747,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>2</v>
+      </c>
+      <c r="E282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20974,7 +21823,10 @@
       <c r="D283" s="4">
         <v>2</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="4">
+        <v>2</v>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21043,9 +21895,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>3</v>
+      </c>
+      <c r="E284" s="4">
         <v>1</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21106,9 +21961,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>3</v>
+      </c>
+      <c r="E285" s="4">
         <v>2</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21171,7 +22029,10 @@
       <c r="D286" s="4">
         <v>3</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="4">
+        <v>3</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21270,9 +22131,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>3</v>
+      </c>
+      <c r="E287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21333,9 +22197,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>3</v>
+      </c>
+      <c r="E288" s="4">
         <v>2</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21413,7 +22280,10 @@
       <c r="D289" s="4">
         <v>3</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="E289" s="4">
+        <v>3</v>
+      </c>
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21482,9 +22352,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>10</v>
+      </c>
+      <c r="E290" s="4">
         <v>1</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21560,9 +22433,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>10</v>
+      </c>
+      <c r="E291" s="4">
         <v>2</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21668,9 +22544,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>10</v>
+      </c>
+      <c r="E292" s="4">
         <v>3</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21739,9 +22618,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>10</v>
+      </c>
+      <c r="E293" s="4">
         <v>4</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21810,9 +22692,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>10</v>
+      </c>
+      <c r="E294" s="4">
         <v>5</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21903,9 +22788,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>10</v>
+      </c>
+      <c r="E295" s="4">
         <v>6</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21981,9 +22869,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>10</v>
+      </c>
+      <c r="E296" s="4">
         <v>7</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22097,9 +22988,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>10</v>
+      </c>
+      <c r="E297" s="4">
         <v>8</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22168,9 +23062,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>10</v>
+      </c>
+      <c r="E298" s="4">
         <v>9</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22241,7 +23138,10 @@
       <c r="D299" s="4">
         <v>10</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="E299" s="4">
+        <v>10</v>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22325,9 +23225,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>7</v>
+      </c>
+      <c r="E300" s="4">
         <v>1</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22388,9 +23291,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>7</v>
+      </c>
+      <c r="E301" s="4">
         <v>2</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22451,9 +23357,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>7</v>
+      </c>
+      <c r="E302" s="4">
         <v>3</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22514,9 +23423,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>7</v>
+      </c>
+      <c r="E303" s="4">
         <v>4</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22577,9 +23489,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>7</v>
+      </c>
+      <c r="E304" s="4">
         <v>5</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22640,9 +23555,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>7</v>
+      </c>
+      <c r="E305" s="4">
         <v>6</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22705,7 +23623,10 @@
       <c r="D306" s="4">
         <v>7</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="E306" s="4">
+        <v>7</v>
+      </c>
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22766,9 +23687,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>20</v>
+      </c>
+      <c r="E307" s="4">
         <v>1</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22838,9 +23762,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>20</v>
+      </c>
+      <c r="E308" s="4">
         <v>2</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22910,9 +23837,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>20</v>
+      </c>
+      <c r="E309" s="4">
         <v>3</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22982,9 +23912,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>20</v>
+      </c>
+      <c r="E310" s="4">
         <v>4</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23054,9 +23987,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>20</v>
+      </c>
+      <c r="E311" s="4">
         <v>5</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23126,9 +24062,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>20</v>
+      </c>
+      <c r="E312" s="4">
         <v>6</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23198,9 +24137,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>20</v>
+      </c>
+      <c r="E313" s="4">
         <v>7</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23270,9 +24212,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>20</v>
+      </c>
+      <c r="E314" s="4">
         <v>8</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23342,9 +24287,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>20</v>
+      </c>
+      <c r="E315" s="4">
         <v>9</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23414,9 +24362,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>20</v>
+      </c>
+      <c r="E316" s="4">
         <v>10</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23486,9 +24437,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>20</v>
+      </c>
+      <c r="E317" s="4">
         <v>11</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23558,9 +24512,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>20</v>
+      </c>
+      <c r="E318" s="4">
         <v>12</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23630,9 +24587,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>20</v>
+      </c>
+      <c r="E319" s="4">
         <v>13</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23702,9 +24662,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>20</v>
+      </c>
+      <c r="E320" s="4">
         <v>14</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23774,9 +24737,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>20</v>
+      </c>
+      <c r="E321" s="4">
         <v>15</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23846,9 +24812,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>20</v>
+      </c>
+      <c r="E322" s="4">
         <v>16</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23918,9 +24887,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>20</v>
+      </c>
+      <c r="E323" s="4">
         <v>17</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23990,9 +24962,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>20</v>
+      </c>
+      <c r="E324" s="4">
         <v>18</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24062,9 +25037,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>63</v>
+      </c>
+      <c r="E325" s="4">
         <v>1</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24134,9 +25112,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>63</v>
+      </c>
+      <c r="E326" s="4">
         <v>2</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24206,9 +25187,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>63</v>
+      </c>
+      <c r="E327" s="4">
         <v>3</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24278,9 +25262,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>63</v>
+      </c>
+      <c r="E328" s="4">
         <v>4</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24350,9 +25337,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>63</v>
+      </c>
+      <c r="E329" s="4">
         <v>5</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24422,9 +25412,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>63</v>
+      </c>
+      <c r="E330" s="4">
         <v>6</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24494,9 +25487,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>63</v>
+      </c>
+      <c r="E331" s="4">
         <v>7</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24566,9 +25562,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>63</v>
+      </c>
+      <c r="E332" s="4">
         <v>8</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24638,9 +25637,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>63</v>
+      </c>
+      <c r="E333" s="4">
         <v>9</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24710,9 +25712,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>63</v>
+      </c>
+      <c r="E334" s="4">
         <v>10</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24782,9 +25787,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>63</v>
+      </c>
+      <c r="E335" s="4">
         <v>11</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24854,9 +25862,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>63</v>
+      </c>
+      <c r="E336" s="4">
         <v>12</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24917,9 +25928,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>63</v>
+      </c>
+      <c r="E337" s="4">
         <v>13</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24989,9 +26003,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>63</v>
+      </c>
+      <c r="E338" s="4">
         <v>14</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25061,9 +26078,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>63</v>
+      </c>
+      <c r="E339" s="4">
         <v>15</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25133,9 +26153,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>63</v>
+      </c>
+      <c r="E340" s="4">
         <v>16</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25205,9 +26228,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>63</v>
+      </c>
+      <c r="E341" s="4">
         <v>17</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25277,9 +26303,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>63</v>
+      </c>
+      <c r="E342" s="4">
         <v>18</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25349,9 +26378,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>63</v>
+      </c>
+      <c r="E343" s="4">
         <v>19</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25421,9 +26453,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>63</v>
+      </c>
+      <c r="E344" s="4">
         <v>20</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25495,7 +26530,10 @@
       <c r="D345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="E345" s="4">
+        <v>1</v>
+      </c>
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25551,7 +26589,10 @@
       <c r="D346" s="4">
         <v>1</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="E346" s="4">
+        <v>1</v>
+      </c>
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25605,9 +26646,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>2</v>
+      </c>
+      <c r="E347" s="4">
         <v>1</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25663,7 +26707,10 @@
       <c r="D348" s="4">
         <v>2</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="E348" s="4">
+        <v>2</v>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25717,9 +26764,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>3</v>
+      </c>
+      <c r="E349" s="4">
         <v>1</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25773,9 +26823,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>3</v>
+      </c>
+      <c r="E350" s="4">
         <v>2</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25831,7 +26884,10 @@
       <c r="D351" s="4">
         <v>3</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="E351" s="4">
+        <v>3</v>
+      </c>
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25885,9 +26941,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>2</v>
+      </c>
+      <c r="E352" s="4">
         <v>1</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25943,7 +27002,10 @@
       <c r="D353" s="4">
         <v>2</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="E353" s="4">
+        <v>2</v>
+      </c>
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25997,9 +27059,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>26</v>
+      </c>
+      <c r="E354" s="4">
         <v>1</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26053,9 +27118,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>26</v>
+      </c>
+      <c r="E355" s="4">
         <v>2</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26109,9 +27177,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>26</v>
+      </c>
+      <c r="E356" s="4">
         <v>3</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26165,9 +27236,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>26</v>
+      </c>
+      <c r="E357" s="4">
         <v>4</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26221,9 +27295,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>26</v>
+      </c>
+      <c r="E358" s="4">
         <v>5</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26277,9 +27354,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>26</v>
+      </c>
+      <c r="E359" s="4">
         <v>6</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26333,9 +27413,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>26</v>
+      </c>
+      <c r="E360" s="4">
         <v>7</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26389,9 +27472,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>26</v>
+      </c>
+      <c r="E361" s="4">
         <v>8</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26445,9 +27531,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>26</v>
+      </c>
+      <c r="E362" s="4">
         <v>9</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26501,9 +27590,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>26</v>
+      </c>
+      <c r="E363" s="4">
         <v>10</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26557,9 +27649,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>26</v>
+      </c>
+      <c r="E364" s="4">
         <v>11</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26613,9 +27708,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>26</v>
+      </c>
+      <c r="E365" s="4">
         <v>12</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26669,9 +27767,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>26</v>
+      </c>
+      <c r="E366" s="4">
         <v>13</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26725,9 +27826,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>26</v>
+      </c>
+      <c r="E367" s="4">
         <v>14</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26781,9 +27885,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>26</v>
+      </c>
+      <c r="E368" s="4">
         <v>15</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26837,9 +27944,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>26</v>
+      </c>
+      <c r="E369" s="4">
         <v>16</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26893,9 +28003,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>26</v>
+      </c>
+      <c r="E370" s="4">
         <v>17</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26949,9 +28062,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>26</v>
+      </c>
+      <c r="E371" s="4">
         <v>18</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27005,9 +28121,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>26</v>
+      </c>
+      <c r="E372" s="4">
         <v>19</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27061,9 +28180,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>26</v>
+      </c>
+      <c r="E373" s="4">
         <v>20</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27119,7 +28241,10 @@
       <c r="D374" s="4">
         <v>1</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="E374" s="4">
+        <v>1</v>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27189,9 +28314,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>2</v>
+      </c>
+      <c r="E375" s="4">
         <v>1</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27254,7 +28382,10 @@
       <c r="D376" s="4">
         <v>2</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="E376" s="4">
+        <v>2</v>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27315,9 +28446,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>4</v>
+      </c>
+      <c r="E377" s="4">
         <v>1</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27416,9 +28550,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>4</v>
+      </c>
+      <c r="E378" s="4">
         <v>2</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27517,9 +28654,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>4</v>
+      </c>
+      <c r="E379" s="4">
         <v>3</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27605,7 +28745,10 @@
       <c r="D380" s="4">
         <v>4</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="E380" s="4">
+        <v>4</v>
+      </c>
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27706,7 +28849,10 @@
       <c r="D381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="E381" s="4">
+        <v>1</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27775,9 +28921,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>2</v>
+      </c>
+      <c r="E382" s="4">
         <v>1</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27863,7 +29012,10 @@
       <c r="D383" s="4">
         <v>2</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>2</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27947,9 +29099,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>12</v>
+      </c>
+      <c r="E384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28145,9 +29300,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>12</v>
+      </c>
+      <c r="E385" s="4">
         <v>2</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28343,9 +29501,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>12</v>
+      </c>
+      <c r="E386" s="4">
         <v>3</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28451,9 +29612,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>12</v>
+      </c>
+      <c r="E387" s="4">
         <v>4</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28559,9 +29723,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>12</v>
+      </c>
+      <c r="E388" s="4">
         <v>5</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28652,9 +29819,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>12</v>
+      </c>
+      <c r="E389" s="4">
         <v>6</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28753,9 +29923,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>12</v>
+      </c>
+      <c r="E390" s="4">
         <v>7</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28876,9 +30049,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>12</v>
+      </c>
+      <c r="E391" s="4">
         <v>8</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29037,9 +30213,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>12</v>
+      </c>
+      <c r="E392" s="4">
         <v>9</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29153,9 +30332,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>12</v>
+      </c>
+      <c r="E393" s="4">
         <v>10</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29261,9 +30443,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>12</v>
+      </c>
+      <c r="E394" s="4">
         <v>11</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29431,7 +30616,10 @@
       <c r="D395" s="4">
         <v>12</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="E395" s="4">
+        <v>12</v>
+      </c>
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29627,9 +30815,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>4</v>
+      </c>
+      <c r="E396" s="4">
         <v>1</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29705,9 +30896,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>4</v>
+      </c>
+      <c r="E397" s="4">
         <v>2</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29776,9 +30970,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>4</v>
+      </c>
+      <c r="E398" s="4">
         <v>3</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29849,7 +31046,10 @@
       <c r="D399" s="4">
         <v>4</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="E399" s="4">
+        <v>4</v>
+      </c>
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29927,7 +31127,10 @@
       <c r="D400" s="4">
         <v>1</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="E400" s="4">
+        <v>1</v>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29990,7 +31193,10 @@
       <c r="D401" s="4">
         <v>1</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="4">
+        <v>1</v>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30068,7 +31274,10 @@
       <c r="D402" s="4">
         <v>1</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="4">
+        <v>1</v>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30221,7 +31430,10 @@
       <c r="D403" s="4">
         <v>1</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="4">
+        <v>1</v>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30292,7 +31504,10 @@
       <c r="D404" s="4">
         <v>1</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="E404" s="4">
+        <v>1</v>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30443,9 +31658,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>7</v>
+      </c>
+      <c r="E405" s="4">
         <v>1</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30506,9 +31724,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>7</v>
+      </c>
+      <c r="E406" s="4">
         <v>2</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30569,9 +31790,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>7</v>
+      </c>
+      <c r="E407" s="4">
         <v>3</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30632,9 +31856,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>7</v>
+      </c>
+      <c r="E408" s="4">
         <v>4</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30695,9 +31922,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>7</v>
+      </c>
+      <c r="E409" s="4">
         <v>5</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30758,9 +31988,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>7</v>
+      </c>
+      <c r="E410" s="4">
         <v>6</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30823,7 +32056,10 @@
       <c r="D411" s="4">
         <v>7</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="E411" s="4">
+        <v>7</v>
+      </c>
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30884,9 +32120,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>2</v>
+      </c>
+      <c r="E412" s="4">
         <v>1</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30964,7 +32203,10 @@
       <c r="D413" s="4">
         <v>2</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="E413" s="4">
+        <v>2</v>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31042,7 +32284,10 @@
       <c r="D414" s="4">
         <v>1</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="E414" s="4">
+        <v>1</v>
+      </c>
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31126,9 +32371,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>5</v>
+      </c>
+      <c r="E415" s="4">
         <v>1</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31272,9 +32520,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>5</v>
+      </c>
+      <c r="E416" s="4">
         <v>2</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31365,9 +32616,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>5</v>
+      </c>
+      <c r="E417" s="4">
         <v>3</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31511,9 +32765,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>5</v>
+      </c>
+      <c r="E418" s="4">
         <v>4</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31644,7 +32901,10 @@
       <c r="D419" s="4">
         <v>5</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="4">
+        <v>5</v>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31782,7 +33042,10 @@
       <c r="D420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="E420" s="4">
+        <v>1</v>
+      </c>
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31845,7 +33108,10 @@
       <c r="D421" s="4">
         <v>1</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="4">
+        <v>1</v>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31906,9 +33172,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>11</v>
+      </c>
+      <c r="E422" s="4">
         <v>1</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31969,9 +33238,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>11</v>
+      </c>
+      <c r="E423" s="4">
         <v>2</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32032,9 +33304,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>11</v>
+      </c>
+      <c r="E424" s="4">
         <v>3</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32095,9 +33370,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>11</v>
+      </c>
+      <c r="E425" s="4">
         <v>4</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32158,9 +33436,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>11</v>
+      </c>
+      <c r="E426" s="4">
         <v>5</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32230,9 +33511,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>11</v>
+      </c>
+      <c r="E427" s="4">
         <v>6</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32293,9 +33577,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>11</v>
+      </c>
+      <c r="E428" s="4">
         <v>7</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32356,9 +33643,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>11</v>
+      </c>
+      <c r="E429" s="4">
         <v>8</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32419,9 +33709,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>11</v>
+      </c>
+      <c r="E430" s="4">
         <v>9</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32482,9 +33775,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>11</v>
+      </c>
+      <c r="E431" s="4">
         <v>10</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32547,7 +33843,10 @@
       <c r="D432" s="4">
         <v>11</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="4">
+        <v>11</v>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32617,9 +33916,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>13</v>
+      </c>
+      <c r="E433" s="4">
         <v>1</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32680,9 +33982,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>13</v>
+      </c>
+      <c r="E434" s="4">
         <v>2</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32743,9 +34048,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>13</v>
+      </c>
+      <c r="E435" s="4">
         <v>3</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32806,9 +34114,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>13</v>
+      </c>
+      <c r="E436" s="4">
         <v>4</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32869,9 +34180,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>13</v>
+      </c>
+      <c r="E437" s="4">
         <v>5</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32932,9 +34246,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>13</v>
+      </c>
+      <c r="E438" s="4">
         <v>6</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32995,9 +34312,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>13</v>
+      </c>
+      <c r="E439" s="4">
         <v>7</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33058,9 +34378,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>13</v>
+      </c>
+      <c r="E440" s="4">
         <v>8</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33121,9 +34444,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>13</v>
+      </c>
+      <c r="E441" s="4">
         <v>9</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33184,9 +34510,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>13</v>
+      </c>
+      <c r="E442" s="4">
         <v>10</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33247,9 +34576,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>13</v>
+      </c>
+      <c r="E443" s="4">
         <v>11</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33310,9 +34642,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>13</v>
+      </c>
+      <c r="E444" s="4">
         <v>12</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33375,7 +34710,10 @@
       <c r="D445" s="4">
         <v>13</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="E445" s="4">
+        <v>13</v>
+      </c>
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33438,7 +34776,10 @@
       <c r="D446" s="4">
         <v>1</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="E446" s="4">
+        <v>1</v>
+      </c>
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33507,9 +34848,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>3</v>
+      </c>
+      <c r="E447" s="4">
         <v>1</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33585,9 +34929,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>3</v>
+      </c>
+      <c r="E448" s="4">
         <v>2</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33665,7 +35012,10 @@
       <c r="D449" s="4">
         <v>3</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="4">
+        <v>3</v>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33741,9 +35091,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>9</v>
+      </c>
+      <c r="E450" s="4">
         <v>1</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33804,9 +35157,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>9</v>
+      </c>
+      <c r="E451" s="4">
         <v>2</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33875,9 +35231,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>9</v>
+      </c>
+      <c r="E452" s="4">
         <v>3</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33938,9 +35297,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>9</v>
+      </c>
+      <c r="E453" s="4">
         <v>4</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34001,9 +35363,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>9</v>
+      </c>
+      <c r="E454" s="4">
         <v>5</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34079,9 +35444,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>9</v>
+      </c>
+      <c r="E455" s="4">
         <v>6</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34142,9 +35510,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>9</v>
+      </c>
+      <c r="E456" s="4">
         <v>7</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34205,9 +35576,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>9</v>
+      </c>
+      <c r="E457" s="4">
         <v>8</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34270,7 +35644,10 @@
       <c r="D458" s="4">
         <v>9</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="E458" s="4">
+        <v>9</v>
+      </c>
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34361,9 +35738,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>3</v>
+      </c>
+      <c r="E459" s="4">
         <v>1</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34433,9 +35813,12 @@
         </is>
       </c>
       <c r="D460" s="4">
+        <v>3</v>
+      </c>
+      <c r="E460" s="4">
         <v>2</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34507,7 +35890,10 @@
       <c r="D461" s="4">
         <v>3</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="E461" s="4">
+        <v>3</v>
+      </c>
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34577,9 +35963,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>2</v>
+      </c>
+      <c r="E462" s="4">
         <v>1</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34651,7 +36040,10 @@
       <c r="D463" s="4">
         <v>2</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="4">
+        <v>2</v>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34712,9 +36104,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>2</v>
+      </c>
+      <c r="E464" s="4">
         <v>1</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34786,7 +36181,10 @@
       <c r="D465" s="4">
         <v>2</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="E465" s="4">
+        <v>2</v>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34856,9 +36254,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>6</v>
+      </c>
+      <c r="E466" s="4">
         <v>1</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34928,9 +36329,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>6</v>
+      </c>
+      <c r="E467" s="4">
         <v>2</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35000,9 +36404,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>6</v>
+      </c>
+      <c r="E468" s="4">
         <v>3</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35072,9 +36479,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>6</v>
+      </c>
+      <c r="E469" s="4">
         <v>4</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35144,9 +36554,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>6</v>
+      </c>
+      <c r="E470" s="4">
         <v>5</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35218,7 +36631,10 @@
       <c r="D471" s="4">
         <v>6</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="E471" s="4">
+        <v>6</v>
+      </c>
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35288,9 +36704,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>7</v>
+      </c>
+      <c r="E472" s="4">
         <v>1</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35360,9 +36779,12 @@
         </is>
       </c>
       <c r="D473" s="4">
+        <v>7</v>
+      </c>
+      <c r="E473" s="4">
         <v>2</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35432,9 +36854,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>7</v>
+      </c>
+      <c r="E474" s="4">
         <v>3</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35504,9 +36929,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>7</v>
+      </c>
+      <c r="E475" s="4">
         <v>4</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35567,9 +36995,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>7</v>
+      </c>
+      <c r="E476" s="4">
         <v>5</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35639,9 +37070,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>7</v>
+      </c>
+      <c r="E477" s="4">
         <v>6</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35711,9 +37145,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>3</v>
+      </c>
+      <c r="E478" s="4">
         <v>1</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35783,9 +37220,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>3</v>
+      </c>
+      <c r="E479" s="4">
         <v>2</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35855,9 +37295,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>2</v>
+      </c>
+      <c r="E480" s="4">
         <v>1</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35929,7 +37372,10 @@
       <c r="D481" s="4">
         <v>2</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="E481" s="4">
+        <v>2</v>
+      </c>
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36001,7 +37447,10 @@
       <c r="D482" s="4">
         <v>1</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="E482" s="4">
+        <v>1</v>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36071,9 +37520,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>3</v>
+      </c>
+      <c r="E483" s="4">
         <v>1</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36143,9 +37595,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>3</v>
+      </c>
+      <c r="E484" s="4">
         <v>2</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36217,7 +37672,10 @@
       <c r="D485" s="4">
         <v>3</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="E485" s="4">
+        <v>3</v>
+      </c>
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36289,7 +37747,10 @@
       <c r="D486" s="4">
         <v>1</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="E486" s="4">
+        <v>1</v>
+      </c>
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36361,7 +37822,10 @@
       <c r="D487" s="4">
         <v>1</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="E487" s="4">
+        <v>1</v>
+      </c>
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36433,7 +37897,10 @@
       <c r="D488" s="4">
         <v>1</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="E488" s="4">
+        <v>1</v>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36494,9 +37961,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>11</v>
+      </c>
+      <c r="E489" s="4">
         <v>1</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36566,9 +38036,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>11</v>
+      </c>
+      <c r="E490" s="4">
         <v>2</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36638,9 +38111,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>11</v>
+      </c>
+      <c r="E491" s="4">
         <v>3</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36710,9 +38186,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>11</v>
+      </c>
+      <c r="E492" s="4">
         <v>4</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36782,9 +38261,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>11</v>
+      </c>
+      <c r="E493" s="4">
         <v>5</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36854,9 +38336,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>11</v>
+      </c>
+      <c r="E494" s="4">
         <v>6</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36926,9 +38411,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>11</v>
+      </c>
+      <c r="E495" s="4">
         <v>7</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36998,9 +38486,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>11</v>
+      </c>
+      <c r="E496" s="4">
         <v>8</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37070,9 +38561,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>11</v>
+      </c>
+      <c r="E497" s="4">
         <v>9</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37142,9 +38636,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>11</v>
+      </c>
+      <c r="E498" s="4">
         <v>10</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37216,7 +38713,10 @@
       <c r="D499" s="4">
         <v>11</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="E499" s="4">
+        <v>11</v>
+      </c>
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37286,9 +38786,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>14</v>
+      </c>
+      <c r="E500" s="4">
         <v>1</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37358,9 +38861,12 @@
         </is>
       </c>
       <c r="D501" s="4">
+        <v>14</v>
+      </c>
+      <c r="E501" s="4">
         <v>2</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37430,9 +38936,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>14</v>
+      </c>
+      <c r="E502" s="4">
         <v>3</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37502,9 +39011,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>14</v>
+      </c>
+      <c r="E503" s="4">
         <v>4</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37574,9 +39086,12 @@
         </is>
       </c>
       <c r="D504" s="4">
+        <v>14</v>
+      </c>
+      <c r="E504" s="4">
         <v>5</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37646,9 +39161,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>14</v>
+      </c>
+      <c r="E505" s="4">
         <v>6</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37718,9 +39236,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>14</v>
+      </c>
+      <c r="E506" s="4">
         <v>7</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37790,9 +39311,12 @@
         </is>
       </c>
       <c r="D507" s="4">
+        <v>14</v>
+      </c>
+      <c r="E507" s="4">
         <v>8</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37862,9 +39386,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>14</v>
+      </c>
+      <c r="E508" s="4">
         <v>9</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37934,9 +39461,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>14</v>
+      </c>
+      <c r="E509" s="4">
         <v>10</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38006,9 +39536,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>14</v>
+      </c>
+      <c r="E510" s="4">
         <v>11</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38078,9 +39611,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>14</v>
+      </c>
+      <c r="E511" s="4">
         <v>12</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38150,9 +39686,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>14</v>
+      </c>
+      <c r="E512" s="4">
         <v>13</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38224,7 +39763,10 @@
       <c r="D513" s="4">
         <v>14</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="E513" s="4">
+        <v>14</v>
+      </c>
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38294,9 +39836,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>3</v>
+      </c>
+      <c r="E514" s="4">
         <v>1</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38366,9 +39911,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>3</v>
+      </c>
+      <c r="E515" s="4">
         <v>2</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38440,7 +39988,10 @@
       <c r="D516" s="4">
         <v>3</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="E516" s="4">
+        <v>3</v>
+      </c>
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38510,9 +40061,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>2</v>
+      </c>
+      <c r="E517" s="4">
         <v>1</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38575,7 +40129,10 @@
       <c r="D518" s="4">
         <v>2</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="4">
+        <v>2</v>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38645,9 +40202,12 @@
         </is>
       </c>
       <c r="D519" s="4">
+        <v>2</v>
+      </c>
+      <c r="E519" s="4">
         <v>1</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38719,7 +40279,10 @@
       <c r="D520" s="4">
         <v>2</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="E520" s="4">
+        <v>2</v>
+      </c>
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38789,9 +40352,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>6</v>
+      </c>
+      <c r="E521" s="4">
         <v>1</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38861,9 +40427,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>6</v>
+      </c>
+      <c r="E522" s="4">
         <v>2</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38933,9 +40502,12 @@
         </is>
       </c>
       <c r="D523" s="4">
+        <v>6</v>
+      </c>
+      <c r="E523" s="4">
         <v>3</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38996,9 +40568,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>6</v>
+      </c>
+      <c r="E524" s="4">
         <v>4</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39068,9 +40643,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>6</v>
+      </c>
+      <c r="E525" s="4">
         <v>5</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39142,7 +40720,10 @@
       <c r="D526" s="4">
         <v>6</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="E526" s="4">
+        <v>6</v>
+      </c>
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39196,253 +40777,335 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="246">
+  <mergeCells count="328">
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C30:C33"/>
+    <mergeCell ref="D30:D33"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="B44:B45"/>
     <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
     <mergeCell ref="A49:A50"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
     <mergeCell ref="A63:A67"/>
     <mergeCell ref="B63:B67"/>
     <mergeCell ref="C63:C67"/>
+    <mergeCell ref="D63:D67"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
     <mergeCell ref="C74:C75"/>
+    <mergeCell ref="D74:D75"/>
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="B82:B83"/>
     <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
     <mergeCell ref="A84:A85"/>
     <mergeCell ref="B84:B85"/>
     <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="B92:B93"/>
     <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="A117:A118"/>
     <mergeCell ref="B117:B118"/>
     <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
     <mergeCell ref="A134:A135"/>
     <mergeCell ref="B134:B135"/>
     <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
     <mergeCell ref="A139:A142"/>
     <mergeCell ref="B139:B142"/>
     <mergeCell ref="C139:C142"/>
+    <mergeCell ref="D139:D142"/>
     <mergeCell ref="A151:A152"/>
     <mergeCell ref="B151:B152"/>
     <mergeCell ref="C151:C152"/>
+    <mergeCell ref="D151:D152"/>
     <mergeCell ref="A155:A156"/>
     <mergeCell ref="B155:B156"/>
     <mergeCell ref="C155:C156"/>
+    <mergeCell ref="D155:D156"/>
     <mergeCell ref="A160:A162"/>
     <mergeCell ref="B160:B162"/>
     <mergeCell ref="C160:C162"/>
+    <mergeCell ref="D160:D162"/>
     <mergeCell ref="A164:A165"/>
     <mergeCell ref="B164:B165"/>
     <mergeCell ref="C164:C165"/>
+    <mergeCell ref="D164:D165"/>
     <mergeCell ref="A183:A185"/>
     <mergeCell ref="B183:B185"/>
     <mergeCell ref="C183:C185"/>
+    <mergeCell ref="D183:D185"/>
     <mergeCell ref="A186:A190"/>
     <mergeCell ref="B186:B190"/>
     <mergeCell ref="C186:C190"/>
+    <mergeCell ref="D186:D190"/>
     <mergeCell ref="A191:A192"/>
     <mergeCell ref="B191:B192"/>
     <mergeCell ref="C191:C192"/>
+    <mergeCell ref="D191:D192"/>
     <mergeCell ref="A193:A198"/>
     <mergeCell ref="B193:B198"/>
     <mergeCell ref="C193:C198"/>
+    <mergeCell ref="D193:D198"/>
     <mergeCell ref="A199:A201"/>
     <mergeCell ref="B199:B201"/>
     <mergeCell ref="C199:C201"/>
+    <mergeCell ref="D199:D201"/>
     <mergeCell ref="A202:A203"/>
     <mergeCell ref="B202:B203"/>
     <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
     <mergeCell ref="A204:A208"/>
     <mergeCell ref="B204:B208"/>
     <mergeCell ref="C204:C208"/>
+    <mergeCell ref="D204:D208"/>
     <mergeCell ref="A209:A212"/>
     <mergeCell ref="B209:B212"/>
     <mergeCell ref="C209:C212"/>
+    <mergeCell ref="D209:D212"/>
     <mergeCell ref="A213:A214"/>
     <mergeCell ref="B213:B214"/>
     <mergeCell ref="C213:C214"/>
+    <mergeCell ref="D213:D214"/>
     <mergeCell ref="A215:A220"/>
     <mergeCell ref="B215:B220"/>
     <mergeCell ref="C215:C220"/>
+    <mergeCell ref="D215:D220"/>
     <mergeCell ref="A221:A231"/>
     <mergeCell ref="B221:B231"/>
     <mergeCell ref="C221:C231"/>
+    <mergeCell ref="D221:D231"/>
     <mergeCell ref="A233:A234"/>
     <mergeCell ref="B233:B234"/>
     <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
     <mergeCell ref="A235:A254"/>
     <mergeCell ref="B235:B254"/>
     <mergeCell ref="C235:C254"/>
+    <mergeCell ref="D235:D254"/>
     <mergeCell ref="A255:A258"/>
     <mergeCell ref="B255:B258"/>
     <mergeCell ref="C255:C258"/>
+    <mergeCell ref="D255:D258"/>
     <mergeCell ref="A260:A261"/>
     <mergeCell ref="B260:B261"/>
     <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
     <mergeCell ref="A262:A263"/>
     <mergeCell ref="B262:B263"/>
     <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
     <mergeCell ref="A264:A274"/>
     <mergeCell ref="B264:B274"/>
     <mergeCell ref="C264:C274"/>
+    <mergeCell ref="D264:D274"/>
     <mergeCell ref="A275:A276"/>
     <mergeCell ref="B275:B276"/>
     <mergeCell ref="C275:C276"/>
+    <mergeCell ref="D275:D276"/>
     <mergeCell ref="A278:A280"/>
     <mergeCell ref="B278:B280"/>
     <mergeCell ref="C278:C280"/>
+    <mergeCell ref="D278:D280"/>
     <mergeCell ref="A282:A283"/>
     <mergeCell ref="B282:B283"/>
     <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
     <mergeCell ref="A284:A286"/>
     <mergeCell ref="B284:B286"/>
     <mergeCell ref="C284:C286"/>
+    <mergeCell ref="D284:D286"/>
     <mergeCell ref="A287:A289"/>
     <mergeCell ref="B287:B289"/>
     <mergeCell ref="C287:C289"/>
+    <mergeCell ref="D287:D289"/>
     <mergeCell ref="A290:A299"/>
     <mergeCell ref="B290:B299"/>
     <mergeCell ref="C290:C299"/>
+    <mergeCell ref="D290:D299"/>
     <mergeCell ref="A300:A306"/>
     <mergeCell ref="B300:B306"/>
     <mergeCell ref="C300:C306"/>
+    <mergeCell ref="D300:D306"/>
     <mergeCell ref="A307:A324"/>
     <mergeCell ref="B307:B324"/>
     <mergeCell ref="C307:C324"/>
+    <mergeCell ref="D307:D324"/>
     <mergeCell ref="A325:A344"/>
     <mergeCell ref="B325:B344"/>
     <mergeCell ref="C325:C344"/>
+    <mergeCell ref="D325:D344"/>
     <mergeCell ref="A347:A348"/>
     <mergeCell ref="B347:B348"/>
     <mergeCell ref="C347:C348"/>
+    <mergeCell ref="D347:D348"/>
     <mergeCell ref="A349:A351"/>
     <mergeCell ref="B349:B351"/>
     <mergeCell ref="C349:C351"/>
+    <mergeCell ref="D349:D351"/>
     <mergeCell ref="A352:A353"/>
     <mergeCell ref="B352:B353"/>
     <mergeCell ref="C352:C353"/>
+    <mergeCell ref="D352:D353"/>
     <mergeCell ref="A354:A373"/>
     <mergeCell ref="B354:B373"/>
     <mergeCell ref="C354:C373"/>
+    <mergeCell ref="D354:D373"/>
     <mergeCell ref="A375:A376"/>
     <mergeCell ref="B375:B376"/>
     <mergeCell ref="C375:C376"/>
+    <mergeCell ref="D375:D376"/>
     <mergeCell ref="A377:A380"/>
     <mergeCell ref="B377:B380"/>
     <mergeCell ref="C377:C380"/>
+    <mergeCell ref="D377:D380"/>
     <mergeCell ref="A382:A383"/>
     <mergeCell ref="B382:B383"/>
     <mergeCell ref="C382:C383"/>
+    <mergeCell ref="D382:D383"/>
     <mergeCell ref="A384:A395"/>
     <mergeCell ref="B384:B395"/>
     <mergeCell ref="C384:C395"/>
+    <mergeCell ref="D384:D395"/>
     <mergeCell ref="A396:A399"/>
     <mergeCell ref="B396:B399"/>
     <mergeCell ref="C396:C399"/>
+    <mergeCell ref="D396:D399"/>
     <mergeCell ref="A405:A411"/>
     <mergeCell ref="B405:B411"/>
     <mergeCell ref="C405:C411"/>
+    <mergeCell ref="D405:D411"/>
     <mergeCell ref="A412:A413"/>
     <mergeCell ref="B412:B413"/>
     <mergeCell ref="C412:C413"/>
+    <mergeCell ref="D412:D413"/>
     <mergeCell ref="A415:A419"/>
     <mergeCell ref="B415:B419"/>
     <mergeCell ref="C415:C419"/>
+    <mergeCell ref="D415:D419"/>
     <mergeCell ref="A422:A432"/>
     <mergeCell ref="B422:B432"/>
     <mergeCell ref="C422:C432"/>
+    <mergeCell ref="D422:D432"/>
     <mergeCell ref="A433:A445"/>
     <mergeCell ref="B433:B445"/>
     <mergeCell ref="C433:C445"/>
+    <mergeCell ref="D433:D445"/>
     <mergeCell ref="A447:A449"/>
     <mergeCell ref="B447:B449"/>
     <mergeCell ref="C447:C449"/>
+    <mergeCell ref="D447:D449"/>
     <mergeCell ref="A450:A458"/>
     <mergeCell ref="B450:B458"/>
     <mergeCell ref="C450:C458"/>
+    <mergeCell ref="D450:D458"/>
     <mergeCell ref="A459:A461"/>
     <mergeCell ref="B459:B461"/>
     <mergeCell ref="C459:C461"/>
+    <mergeCell ref="D459:D461"/>
     <mergeCell ref="A462:A463"/>
     <mergeCell ref="B462:B463"/>
     <mergeCell ref="C462:C463"/>
+    <mergeCell ref="D462:D463"/>
     <mergeCell ref="A464:A465"/>
     <mergeCell ref="B464:B465"/>
     <mergeCell ref="C464:C465"/>
+    <mergeCell ref="D464:D465"/>
     <mergeCell ref="A466:A471"/>
     <mergeCell ref="B466:B471"/>
     <mergeCell ref="C466:C471"/>
+    <mergeCell ref="D466:D471"/>
     <mergeCell ref="A472:A477"/>
     <mergeCell ref="B472:B477"/>
     <mergeCell ref="C472:C477"/>
+    <mergeCell ref="D472:D477"/>
     <mergeCell ref="A478:A479"/>
     <mergeCell ref="B478:B479"/>
     <mergeCell ref="C478:C479"/>
+    <mergeCell ref="D478:D479"/>
     <mergeCell ref="A480:A481"/>
     <mergeCell ref="B480:B481"/>
     <mergeCell ref="C480:C481"/>
+    <mergeCell ref="D480:D481"/>
     <mergeCell ref="A483:A485"/>
     <mergeCell ref="B483:B485"/>
     <mergeCell ref="C483:C485"/>
+    <mergeCell ref="D483:D485"/>
     <mergeCell ref="A489:A499"/>
     <mergeCell ref="B489:B499"/>
     <mergeCell ref="C489:C499"/>
+    <mergeCell ref="D489:D499"/>
     <mergeCell ref="A500:A513"/>
     <mergeCell ref="B500:B513"/>
     <mergeCell ref="C500:C513"/>
+    <mergeCell ref="D500:D513"/>
     <mergeCell ref="A514:A516"/>
     <mergeCell ref="B514:B516"/>
     <mergeCell ref="C514:C516"/>
+    <mergeCell ref="D514:D516"/>
     <mergeCell ref="A517:A518"/>
     <mergeCell ref="B517:B518"/>
     <mergeCell ref="C517:C518"/>
+    <mergeCell ref="D517:D518"/>
     <mergeCell ref="A519:A520"/>
     <mergeCell ref="B519:B520"/>
     <mergeCell ref="C519:C520"/>
+    <mergeCell ref="D519:D520"/>
     <mergeCell ref="A521:A526"/>
     <mergeCell ref="B521:B526"/>
     <mergeCell ref="C521:C526"/>
+    <mergeCell ref="D521:D526"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
